--- a/Imagenes/Imagenes.xlsx
+++ b/Imagenes/Imagenes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Code\UTN\Tecnicatura superior en Programacion\2025\Laboratorio en Programacion IV\Buen sabor\BuenSaborBack\Documentos\Labo4\archivos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Code\UTN\Tecnicatura superior en Programacion\2025\Laboratorio en Programacion IV\Buen sabor\BuenSaborBack\Imagenes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{182DB7F2-E5F6-4DA9-9625-2949A00FC6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07964CE5-DF35-4878-AEAE-7F54C2DD5D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5145" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{CCE8632C-32BE-425A-965F-607F9D0ACF7C}"/>
   </bookViews>
@@ -35,29 +35,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="71">
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Artículo / Bebida</t>
-  </si>
-  <si>
-    <t>Estado</t>
-  </si>
-  <si>
-    <t>Nombre del archivo (UUID)</t>
-  </si>
-  <si>
-    <t>Hamburguesa</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="167">
   <si>
     <t>Hamburguesa Simple</t>
   </si>
   <si>
-    <t>Reciclar</t>
-  </si>
-  <si>
     <t>0000000d-0000-0000-0000-000000000001</t>
   </si>
   <si>
@@ -85,9 +67,6 @@
     <t>0000000d-0000-0000-0000-000000000005</t>
   </si>
   <si>
-    <t>Pizza</t>
-  </si>
-  <si>
     <t>Pizza Muzzarella</t>
   </si>
   <si>
@@ -118,27 +97,9 @@
     <t>0000000d-0000-0000-0000-000000000010</t>
   </si>
   <si>
-    <t>Lomo</t>
-  </si>
-  <si>
     <t>Lomo Simple</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">⚠️ </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>NUEVA</t>
-    </r>
-  </si>
-  <si>
     <t>0000000d-0000-0000-0000-000000000011</t>
   </si>
   <si>
@@ -154,9 +115,6 @@
     <t>0000000d-0000-0000-0000-000000000013</t>
   </si>
   <si>
-    <t>Papas</t>
-  </si>
-  <si>
     <t>Porción Papas Fritas</t>
   </si>
   <si>
@@ -169,9 +127,6 @@
     <t>0000000d-0000-0000-0000-000000000015</t>
   </si>
   <si>
-    <t>Bebida</t>
-  </si>
-  <si>
     <t>Coca Cola 500ml</t>
   </si>
   <si>
@@ -260,6 +215,327 @@
   </si>
   <si>
     <t>0000000b-0000-0000-0000-000000000055</t>
+  </si>
+  <si>
+    <t>ID de Base de Datos</t>
+  </si>
+  <si>
+    <t>Denominación</t>
+  </si>
+  <si>
+    <t>Categoría</t>
+  </si>
+  <si>
+    <t>Hamburguesas</t>
+  </si>
+  <si>
+    <t>Pizzas</t>
+  </si>
+  <si>
+    <t>Lomos</t>
+  </si>
+  <si>
+    <t>Guarniciones</t>
+  </si>
+  <si>
+    <t>Es para elaborar</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000001</t>
+  </si>
+  <si>
+    <t>Pan de Hamburguesa</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000002</t>
+  </si>
+  <si>
+    <t>Medallón de Carne 100g</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000003</t>
+  </si>
+  <si>
+    <t>Queso Cheddar</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000004</t>
+  </si>
+  <si>
+    <t>Queso Tybo</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000005</t>
+  </si>
+  <si>
+    <t>Jamón Cocido</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000006</t>
+  </si>
+  <si>
+    <t>Panceta Ahumada</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000007</t>
+  </si>
+  <si>
+    <t>Huevo</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000008</t>
+  </si>
+  <si>
+    <t>Lechuga Repollada</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000009</t>
+  </si>
+  <si>
+    <t>Tomate Perita</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000010</t>
+  </si>
+  <si>
+    <t>Cebolla Blanca</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000011</t>
+  </si>
+  <si>
+    <t>Cebolla Morada</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000012</t>
+  </si>
+  <si>
+    <t>Harina 0000</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000013</t>
+  </si>
+  <si>
+    <t>Levadura Fresca</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000014</t>
+  </si>
+  <si>
+    <t>Salsa de Tomate</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000015</t>
+  </si>
+  <si>
+    <t>Queso Muzzarella</t>
+  </si>
+  <si>
+    <t>Estado de la Promo</t>
+  </si>
+  <si>
+    <t>0000000f-0000-0000-0000-000000000001</t>
+  </si>
+  <si>
+    <t>Promo Burger Simple + Bebida</t>
+  </si>
+  <si>
+    <t>Vigente</t>
+  </si>
+  <si>
+    <t>0000000f-0000-0000-0000-000000000002</t>
+  </si>
+  <si>
+    <t>Promo Pizzas 2x1 (Especial)</t>
+  </si>
+  <si>
+    <t>0000000f-0000-0000-0000-000000000003</t>
+  </si>
+  <si>
+    <t>Promo Lomo Completo + Papas</t>
+  </si>
+  <si>
+    <t>0000000f-0000-0000-0000-000000000004</t>
+  </si>
+  <si>
+    <t>Happy Hour Cerveza</t>
+  </si>
+  <si>
+    <t>0000000f-0000-0000-0000-000000000005</t>
+  </si>
+  <si>
+    <t>Menu Infantil (Burger + Papas)</t>
+  </si>
+  <si>
+    <t>0000000f-0000-0000-0000-000000000006</t>
+  </si>
+  <si>
+    <t>Especial Verano (Bacon + Cerveza)</t>
+  </si>
+  <si>
+    <t>Vencida</t>
+  </si>
+  <si>
+    <t>0000000f-0000-0000-0000-000000000007</t>
+  </si>
+  <si>
+    <t>Promo Vuelta a Clases (Muzza + 2 Cocas)</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000016</t>
+  </si>
+  <si>
+    <t>Aceitunas Verdes</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000017</t>
+  </si>
+  <si>
+    <t>Aceitunas Negras</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000018</t>
+  </si>
+  <si>
+    <t>Orégano</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000019</t>
+  </si>
+  <si>
+    <t>Ajo</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000020</t>
+  </si>
+  <si>
+    <t>Morrón Rojo</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000021</t>
+  </si>
+  <si>
+    <t>Morrón Verde</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000022</t>
+  </si>
+  <si>
+    <t>Aceite de Girasol</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000023</t>
+  </si>
+  <si>
+    <t>Aceite de Oliva</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000024</t>
+  </si>
+  <si>
+    <t>Sal Fina</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000025</t>
+  </si>
+  <si>
+    <t>Pimienta Negra</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000026</t>
+  </si>
+  <si>
+    <t>Pan de Lomo</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000027</t>
+  </si>
+  <si>
+    <t>Carne de Ternera (Lomo)</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000028</t>
+  </si>
+  <si>
+    <t>Pechuga de Pollo</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000029</t>
+  </si>
+  <si>
+    <t>Papa</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000030</t>
+  </si>
+  <si>
+    <t>Batata</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000031</t>
+  </si>
+  <si>
+    <t>Queso Roquefort</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000032</t>
+  </si>
+  <si>
+    <t>Queso Provolone</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000033</t>
+  </si>
+  <si>
+    <t>Salame</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000034</t>
+  </si>
+  <si>
+    <t>Ananá en Almíbar</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000035</t>
+  </si>
+  <si>
+    <t>Palmitos</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000036</t>
+  </si>
+  <si>
+    <t>Salsa Golf</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000037</t>
+  </si>
+  <si>
+    <t>Mayonesa</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000038</t>
+  </si>
+  <si>
+    <t>Ketchup</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000039</t>
+  </si>
+  <si>
+    <t>Mostaza</t>
+  </si>
+  <si>
+    <t>0000000b-0000-0000-0000-000000000040</t>
+  </si>
+  <si>
+    <t>Ají Molido</t>
+  </si>
+  <si>
+    <t>No (Bebida)</t>
   </si>
 </sst>
 </file>
@@ -334,15 +610,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -657,7 +931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B2ABF1E-3625-46FE-A267-7745B8DE57D5}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44.28515625" customWidth="1"/>
@@ -666,438 +940,892 @@
     <col min="4" max="4" width="36.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60.75" thickBot="1">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1">
       <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A2" s="1" t="s">
+      <c r="C3" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="C4" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="C5" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="C6" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="C7" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="C8" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A7" s="1" t="s">
+      <c r="C9" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="C10" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="C11" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="C12" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="C13" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="C14" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="C15" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="C16" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A17" s="1"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A19" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A21" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A22" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A23" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A24" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A28" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A29" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A30" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A31" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A32" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A33" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A34" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A35" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A36" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A37" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A38" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A39" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A40" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A41" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A42" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A43" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A44" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A45" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A46" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A47" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A48" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A49" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A50" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A51" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A52" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A53" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A54" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A55" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A56" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A57" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A58" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="15.75" thickBot="1"/>
+    <row r="60" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="C60" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A61" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="C61" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A62" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A15" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="C62" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A63" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="C63" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A64" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A17" s="1" t="s">
+      <c r="C64" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A65" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="C65" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A66" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="C66" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A67" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="C67" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A68" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A20" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="4" t="s">
+      <c r="C68" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A69" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="C69" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A70" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A22" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="C70" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A23" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="C71" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A72" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="C72" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D72" s="4"/>
+    </row>
+    <row r="73" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A73" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A25" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25" s="4" t="s">
+      <c r="C73" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A74" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B74" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A26" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" s="4" t="s">
+      <c r="C74" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15.75" thickBot="1"/>
+    <row r="76" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A76" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="3" t="s">
+      <c r="B76" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A28" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A29" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A30" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="64.5" thickBot="1">
-      <c r="A31" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>70</v>
+      <c r="C76" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A77" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A78" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A79" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A80" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A81" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A82" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A83" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
